--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487933_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487933_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8423</v>
+        <v>10.6155</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1795</v>
+        <v>10.9233</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3372</v>
+        <v>-0.3078</v>
       </c>
       <c r="G2" t="n">
         <v>9.8635</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2682</v>
+        <v>0.0413</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2701</v>
+        <v>0.0138</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0019</v>
+        <v>0.0275</v>
       </c>
       <c r="V2" t="n">
         <v>1.7513</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8743</v>
+        <v>5.2928</v>
       </c>
       <c r="E3" t="n">
-        <v>4.508</v>
+        <v>4.1027</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3663</v>
+        <v>1.1901</v>
       </c>
       <c r="G3" t="n">
         <v>3.9759</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7308</v>
+        <v>1.1494</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1149</v>
+        <v>0.7096</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6159</v>
+        <v>0.4398</v>
       </c>
       <c r="V3" t="n">
         <v>0.5838</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5489</v>
+        <v>2.9348</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6711</v>
+        <v>3.5486</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2199</v>
+        <v>-0.6138</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2505</v>
+        <v>2.777</v>
       </c>
       <c r="H4" t="n">
-        <v>0.697</v>
+        <v>1.3222</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5535</v>
+        <v>1.4549</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8138</v>
+        <v>4.5815</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3705</v>
+        <v>1.6694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4433</v>
+        <v>2.9122</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4367</v>
+        <v>-1.8045</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3265</v>
+        <v>-0.3472</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1102</v>
+        <v>-1.4573</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.674</v>
+        <v>-0.0504</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4443</v>
+        <v>0.0076</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1183</v>
+        <v>-0.058</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.46</v>
+        <v>2.8884</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1619</v>
+        <v>0.1676</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7019</v>
+        <v>2.7208</v>
       </c>
       <c r="G5" t="n">
-        <v>2.777</v>
+        <v>1.2505</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3222</v>
+        <v>0.697</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4549</v>
+        <v>0.5535</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5815</v>
+        <v>0.8138</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6694</v>
+        <v>0.3705</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9122</v>
+        <v>0.4433</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8045</v>
+        <v>0.4367</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3472</v>
+        <v>0.3265</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4573</v>
+        <v>0.1102</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5252</v>
+        <v>1.0135</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3791</v>
+        <v>0.3944</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1461</v>
+        <v>0.6192</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7236</v>
+        <v>2.4172</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5348</v>
+        <v>0.6387</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8112</v>
+        <v>1.7785</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1296</v>
+        <v>1.9349</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2006</v>
+        <v>0.6483</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9291</v>
+        <v>1.2867</v>
       </c>
       <c r="J6" t="n">
-        <v>3.33</v>
+        <v>1.3921</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9764</v>
+        <v>0.3218</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3536</v>
+        <v>1.0703</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2004</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7758</v>
+        <v>0.3265</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4245</v>
+        <v>0.2164</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1371</v>
+        <v>0.4823</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2454</v>
+        <v>0.2872</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1083</v>
+        <v>0.1951</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7216</v>
+        <v>1.4203</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0276</v>
+        <v>2.0175</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7492</v>
+        <v>-0.5972</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9349</v>
+        <v>1.9926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6483</v>
+        <v>1.9575</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2867</v>
+        <v>0.0351</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3921</v>
+        <v>1.4865</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3218</v>
+        <v>1.631</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0703</v>
+        <v>-0.1445</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5061</v>
       </c>
       <c r="N7" t="n">
         <v>0.3265</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2164</v>
+        <v>0.1796</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2133</v>
+        <v>0.9303</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3791</v>
+        <v>0.531</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1657</v>
+        <v>0.3993</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2988</v>
+        <v>1.4162</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1165</v>
+        <v>2.3972</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1823</v>
+        <v>-0.981</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3791</v>
+        <v>2.0587</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8788</v>
+        <v>2.1558</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4997</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4894</v>
+        <v>2.4548</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1727</v>
+        <v>1.5926</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3167</v>
+        <v>0.8621</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1103</v>
+        <v>-0.3961</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.5632</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8164</v>
+        <v>-0.9593</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>0.336</v>
+        <v>-0.0993</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8539</v>
+        <v>-0.0576</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.518</v>
+        <v>-0.0417</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5838</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1789</v>
+        <v>1.3514</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9523</v>
+        <v>2.9571</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7734</v>
+        <v>-1.6057</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9926</v>
+        <v>2.1296</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9575</v>
+        <v>1.2006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0351</v>
+        <v>0.9291</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4865</v>
+        <v>3.33</v>
       </c>
       <c r="K9" t="n">
-        <v>1.631</v>
+        <v>1.9764</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1445</v>
+        <v>1.3536</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5061</v>
+        <v>-1.2004</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3265</v>
+        <v>-0.7758</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1796</v>
+        <v>-0.4245</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6889</v>
+        <v>0.765</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4658</v>
+        <v>0.6677</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2231</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3351</v>
+        <v>-1.7513</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3351</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.175</v>
+        <v>1.23</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1436</v>
+        <v>1.316</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0314</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>0.719</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0398</v>
+        <v>0.0948</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1072</v>
       </c>
       <c r="U10" t="n">
-        <v>0.105</v>
+        <v>-0.0124</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9708</v>
+        <v>1.1974</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0104</v>
+        <v>0.6041</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0397</v>
+        <v>0.5933</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0587</v>
+        <v>0.3791</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1558</v>
+        <v>0.8788</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.4997</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4548</v>
+        <v>0.4894</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5926</v>
+        <v>0.1727</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8621</v>
+        <v>0.3167</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3961</v>
+        <v>-0.1103</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5632</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9593</v>
+        <v>-0.8164</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5447</v>
+        <v>0.2345</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4443</v>
+        <v>0.3415</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1004</v>
+        <v>-0.107</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1675</v>
+        <v>0.5838</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1309</v>
+        <v>0.1397</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4032</v>
+        <v>1.6176</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2723</v>
+        <v>-1.4779</v>
       </c>
       <c r="G12" t="n">
         <v>0.7803</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0032</v>
+        <v>0.0056</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3138</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3106</v>
+        <v>0.1051</v>
       </c>
       <c r="V12" t="n">
         <v>-0.23</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>29.9251</v>
+        <v>30.9037</v>
       </c>
       <c r="E13" t="n">
-        <v>29.3115</v>
+        <v>30.2904</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6134000000000002</v>
+        <v>0.6133000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>27.8611</v>
@@ -1456,7 +1456,7 @@
         <v>-0.3485000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.204800000000001</v>
+        <v>-6.204799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>1.0407</v>
@@ -1468,13 +1468,13 @@
         <v>11.4465</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5884</v>
+        <v>4.567000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9243</v>
+        <v>2.9029</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6639</v>
+        <v>1.6641</v>
       </c>
       <c r="V13" t="n">
         <v>-2.565</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.618</v>
+        <v>3.2823</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0177</v>
+        <v>3.8471</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3997</v>
+        <v>-0.5647</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.9529</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8124</v>
+        <v>-0.7805</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0572</v>
+        <v>2.7334</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3066</v>
+        <v>3.9451</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1107</v>
+        <v>0.1831</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1959</v>
+        <v>3.7621</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4371</v>
+        <v>-1.9922</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2983</v>
+        <v>-0.9636</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1388</v>
+        <v>-1.0287</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1241</v>
+        <v>0.2888</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7111</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.413</v>
+        <v>0.3869</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5655</v>
+        <v>2.0196</v>
       </c>
       <c r="E15" t="n">
-        <v>3.097</v>
+        <v>2.4819</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5314</v>
+        <v>-0.4624</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9529</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7805</v>
+        <v>0.8124</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7334</v>
+        <v>0.0572</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9451</v>
+        <v>2.3066</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1831</v>
+        <v>2.1107</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7621</v>
+        <v>0.1959</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9922</v>
+        <v>-1.4371</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9636</v>
+        <v>-1.2983</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0287</v>
+        <v>-0.1388</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.428</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8482</v>
+        <v>0.1753</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4202</v>
+        <v>0.3504</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9518</v>
+        <v>1.3295</v>
       </c>
       <c r="E16" t="n">
         <v>3.2905</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3387</v>
+        <v>-1.9609</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7729</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1078</v>
+        <v>-0.7301</v>
       </c>
       <c r="T16" t="n">
         <v>-0.46</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6478</v>
+        <v>-0.2701</v>
       </c>
       <c r="V16" t="n">
         <v>1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6229</v>
+        <v>-0.8666</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2708</v>
+        <v>-0.4851</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3521</v>
+        <v>-0.3815</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7773</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>0.76</v>
+        <v>0.5164</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4534</v>
+        <v>0.2391</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3066</v>
+        <v>0.2773</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8137</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7646</v>
+        <v>-1.9811</v>
       </c>
       <c r="E18" t="n">
-        <v>1.937</v>
+        <v>-1.0215</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.7016</v>
+        <v>-0.9596</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4444</v>
+        <v>-1.1103</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9617</v>
+        <v>-0.0106</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4826</v>
+        <v>-1.0997</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8379</v>
+        <v>0.0776</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.0384</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1176</v>
+        <v>0.0392</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2823</v>
+        <v>-1.1879</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6821</v>
+        <v>-0.049</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6002</v>
+        <v>-1.1389</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>1.096</v>
+        <v>-0.5793</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5559</v>
+        <v>-0.3915</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4599</v>
+        <v>-0.1879</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5838</v>
+        <v>-0.7076</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0398</v>
+        <v>-2.1687</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0215</v>
+        <v>1.3795</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0183</v>
+        <v>-3.5483</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1103</v>
+        <v>-2.3787</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0106</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0997</v>
+        <v>-1.7773</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0776</v>
+        <v>2.1241</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0384</v>
+        <v>0.8399</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0392</v>
+        <v>1.2842</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1879</v>
+        <v>-4.5028</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.049</v>
+        <v>-1.4412</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1389</v>
+        <v>-3.0616</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4162</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6381</v>
+        <v>0.2911</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3915</v>
+        <v>0.1691</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2466</v>
+        <v>0.122</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.272</v>
+        <v>-2.4159</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2724</v>
+        <v>-0.7948</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5443</v>
+        <v>-1.6212</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3787</v>
+        <v>-2.6792</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-1.3305</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7773</v>
+        <v>-1.3487</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1241</v>
+        <v>-0.6176</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8399</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2842</v>
+        <v>0.0392</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.5028</v>
+        <v>-2.0616</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4412</v>
+        <v>-0.6737</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.0616</v>
+        <v>-1.3879</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1879</v>
+        <v>-0.153</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0619</v>
+        <v>-0.1771</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1259</v>
+        <v>0.0242</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4247</v>
+        <v>-2.7124</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0091</v>
+        <v>0.7583</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4157</v>
+        <v>-3.4706</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6792</v>
+        <v>-2.4444</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3305</v>
+        <v>-0.9617</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3487</v>
+        <v>-1.4826</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6176</v>
+        <v>0.8379</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6568000000000001</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0392</v>
+        <v>0.1176</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0616</v>
+        <v>-3.2823</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6737</v>
+        <v>-1.6821</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3879</v>
+        <v>-1.6002</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1618</v>
+        <v>0.1482</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3915</v>
+        <v>0.3772</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2297</v>
+        <v>-0.229</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9525</v>
+        <v>-3.8834</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.538</v>
+        <v>0.2121</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.4145</v>
+        <v>-4.0955</v>
       </c>
       <c r="G22" t="n">
         <v>-4.9208</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5103</v>
+        <v>-0.4412</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9786</v>
+        <v>-0.2286</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5317</v>
+        <v>-0.2127</v>
       </c>
       <c r="V22" t="n">
         <v>0.23</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>G. VERGARA HARBOE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6295</v>
+        <v>-5.2312</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1316</v>
+        <v>-3.3441</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.7611</v>
+        <v>-1.8871</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.0139</v>
+        <v>-4.3688</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3328</v>
+        <v>-2.1856</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6811</v>
+        <v>-2.1831</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6604</v>
+        <v>-1.6009</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6392</v>
+        <v>-0.8383</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0212</v>
+        <v>-0.7625</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.6743</v>
+        <v>-2.7679</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.972</v>
+        <v>-1.3473</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.7023</v>
+        <v>-1.4206</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6244</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1775</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3849</v>
+        <v>-0.8296</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5623</v>
+        <v>-0.1598</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="W23" t="n">
         <v>1.1675</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. VERGARA HARBOE</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6471</v>
+        <v>-5.5771</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5584</v>
+        <v>-0.1899</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0887</v>
+        <v>-5.3872</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.3688</v>
+        <v>-4.0139</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1856</v>
+        <v>-1.3328</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1831</v>
+        <v>-2.6811</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6009</v>
+        <v>0.6604</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8383</v>
+        <v>0.6392</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7625</v>
+        <v>0.0212</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7679</v>
+        <v>-4.6743</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3473</v>
+        <v>-1.972</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4206</v>
+        <v>-2.7023</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0406</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4053</v>
+        <v>-0.1251</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0439</v>
+        <v>0.0634</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3614</v>
+        <v>-0.1885</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1675</v>
+        <v>-0.8137</v>
       </c>
       <c r="W24" t="n">
         <v>1.1675</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.7073</v>
+        <v>-10.2914</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.9618</v>
+        <v>-6.7475</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7455</v>
+        <v>-3.5439</v>
       </c>
       <c r="G25" t="n">
         <v>-7.2173</v>
@@ -2404,13 +2404,13 @@
         <v>0.8325</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3277</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.61</v>
+        <v>-0.4084</v>
       </c>
       <c r="V25" t="n">
         <v>1.1675</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-29.9251</v>
+        <v>-28.4964</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6134000000000013</v>
+        <v>-0.6134999999999984</v>
       </c>
       <c r="F26" t="n">
-        <v>-29.3116</v>
+        <v>-27.8829</v>
       </c>
       <c r="G26" t="n">
         <v>-27.8612</v>
@@ -2482,13 +2482,13 @@
         <v>10.4059</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.5885</v>
+        <v>-2.1597</v>
       </c>
       <c r="T26" t="n">
         <v>-1.6642</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.9243</v>
+        <v>-0.4956</v>
       </c>
       <c r="V26" t="n">
         <v>2.565</v>
